--- a/forms/contact/screening_camp-edit.xlsx
+++ b/forms/contact/screening_camp-edit.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -488,21 +488,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>NO_LABEL</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+          <t>Screening Camp</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>field-list</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -520,18 +513,11 @@
           <t>Camp Name</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -549,18 +535,11 @@
           <t>Location</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -578,11 +557,6 @@
           <t>Contact Number</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>true()</t>
@@ -593,7 +567,6 @@
           <t>Please enter a valid phone number.</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -611,18 +584,11 @@
           <t>Notes</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>multiline</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -630,16 +596,6 @@
           <t>end group</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
